--- a/data/Real.xlsx
+++ b/data/Real.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!MDED\Comert exterior\COD_PAGE\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0867B78-DF48-4B4D-9726-A82571CCD674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F7D801-5F6F-48F5-BC76-7CD73FC3193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4875" yWindow="4005" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Real" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Agricultura" sheetId="9" r:id="rId5"/>
     <sheet name="Industrie_Prel" sheetId="7" r:id="rId6"/>
     <sheet name="Tranport" sheetId="2" r:id="rId7"/>
-    <sheet name="Comert" sheetId="4" r:id="rId8"/>
+    <sheet name="Comert_Intern" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="85">
   <si>
     <t>An</t>
   </si>
@@ -275,6 +275,27 @@
   </si>
   <si>
     <t>Producția animalieră</t>
+  </si>
+  <si>
+    <t>Comert cu ridicata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total comert </t>
+  </si>
+  <si>
+    <t>Comert cu amanuntul</t>
+  </si>
+  <si>
+    <t>Creștere reala comert</t>
+  </si>
+  <si>
+    <t>Crestere reala comert cu amanuntul</t>
+  </si>
+  <si>
+    <t>Crestere reala comert cu ridicata</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -286,7 +307,7 @@
     <numFmt numFmtId="165" formatCode="[$-418]mmmm\-yy;@"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,6 +383,12 @@
       <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -459,7 +486,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -543,6 +570,22 @@
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,6 +604,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -574,6 +618,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -587,6 +632,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -600,6 +646,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -613,6 +660,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -626,6 +674,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -638,6 +687,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -651,6 +701,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -663,6 +714,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -676,6 +728,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -689,9 +742,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="166" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$-418]mmmm\-yy;@"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -704,6 +755,9 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="165" formatCode="[$-418]mmmm\-yy;@"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="165" formatCode="[$-418]mmmm\-yy;@"/>
     </dxf>
     <dxf>
@@ -802,7 +856,7 @@
   <autoFilter ref="A1:M18" xr:uid="{4A6A945B-9F29-4D0C-8A7A-AF2D42CC98E8}"/>
   <tableColumns count="13">
     <tableColumn id="7" xr3:uid="{045D9D44-7F60-4F4E-B61F-3C4A811526D5}" name="An" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{05E6B759-F583-4594-A2AF-6E8346DD0354}" name="Trimestrul" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{05E6B759-F583-4594-A2AF-6E8346DD0354}" name="Trimestrul" dataDxfId="11" totalsRowDxfId="12"/>
     <tableColumn id="2" xr3:uid="{C91398D6-47F0-4A5A-BEA2-B71364BCE39C}" name="Total mărfuri transportate, mii tone" dataDxfId="10"/>
     <tableColumn id="3" xr3:uid="{E18D51A5-C42B-444A-9D0F-BA427D9D332E}" name="Feroviar mărfuri" dataDxfId="9"/>
     <tableColumn id="4" xr3:uid="{47BED2D8-EC79-4C6C-B0F1-269C21B4A651}" name="Rutier mărfuri" dataDxfId="8"/>
@@ -4475,22 +4529,22 @@
       <c r="G2" s="9">
         <v>0.3</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="37">
         <v>45659.199999999997</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="37">
         <v>140.69999999999999</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="37">
         <v>14224.7</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="37">
         <v>52.3</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="37">
         <v>83.8</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="37">
         <v>31157.7</v>
       </c>
     </row>
@@ -4516,22 +4570,22 @@
       <c r="G3" s="9">
         <v>0.4</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="37">
         <v>47648.9</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="37">
         <v>156.5</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="37">
         <v>14701.4</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="37">
         <v>45.7</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="37">
         <v>185.9</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="37">
         <v>32559.4</v>
       </c>
     </row>
@@ -4557,22 +4611,22 @@
       <c r="G4" s="9">
         <v>0.3</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="37">
         <v>51546.8</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="37">
         <v>178.6</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="37">
         <v>15282.3</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="37">
         <v>39</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="37">
         <v>365.4</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="37">
         <v>35681.5</v>
       </c>
     </row>
@@ -4598,22 +4652,22 @@
       <c r="G5" s="9">
         <v>0.4</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="37">
         <v>52124.3</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="37">
         <v>121.8</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="37">
         <v>15048.8</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="37">
         <v>32.200000000000003</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="37">
         <v>203</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="37">
         <v>36718.5</v>
       </c>
     </row>
@@ -4639,22 +4693,22 @@
       <c r="G6" s="9">
         <v>0.3</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="37">
         <v>51749.7</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="37">
         <v>127.1</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="37">
         <v>16098.6</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="37">
         <v>24</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="37">
         <v>107.3</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="37">
         <v>35392.699999999997</v>
       </c>
     </row>
@@ -4680,22 +4734,22 @@
       <c r="G7" s="9">
         <v>0.2</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="37">
         <v>57937.2</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="37">
         <v>145.9</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="37">
         <v>16697.099999999999</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="37">
         <v>60.4</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="37">
         <v>275.3</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="37">
         <v>40758.5</v>
       </c>
     </row>
@@ -4721,22 +4775,22 @@
       <c r="G8" s="9">
         <v>0.3</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="37">
         <v>63910.9</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="37">
         <v>147.9</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="37">
         <v>20972.6</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="37">
         <v>20.399999999999999</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="37">
         <v>507.4</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="37">
         <v>42262.6</v>
       </c>
     </row>
@@ -4762,22 +4816,22 @@
       <c r="G9" s="9">
         <v>0.4</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="37">
         <v>72778.899999999994</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="37">
         <v>151.30000000000001</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="37">
         <v>25700.5</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="37">
         <v>28.4</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="37">
         <v>310.2</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="37">
         <v>46588.5</v>
       </c>
     </row>
@@ -4803,22 +4857,22 @@
       <c r="G10" s="9">
         <v>0.4</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="37">
         <v>67437.2</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="37">
         <v>180.8</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="37">
         <v>20865.099999999999</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="37">
         <v>24.3</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="37">
         <v>249.3</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="37">
         <v>46117.7</v>
       </c>
     </row>
@@ -4844,22 +4898,22 @@
       <c r="G11" s="9">
         <v>0.3</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="37">
         <v>66165.2</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="37">
         <v>181.5</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="37">
         <v>20243.5</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="37">
         <v>44.2</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="37">
         <v>275.7</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="37">
         <v>45420.3</v>
       </c>
     </row>
@@ -4885,22 +4939,22 @@
       <c r="G12" s="9">
         <v>0.3</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="37">
         <v>66536.399999999994</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="37">
         <v>210.5</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="37">
         <v>21345.8</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="37">
         <v>35.5</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="37">
         <v>443.4</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="37">
         <v>44501.2</v>
       </c>
     </row>
@@ -4926,22 +4980,22 @@
       <c r="G13" s="9">
         <v>0.4</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="37">
         <v>73317.5</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="37">
         <v>201.5</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="37">
         <v>22994.400000000001</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="37">
         <v>24.2</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="37">
         <v>290.89999999999998</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="37">
         <v>49806.5</v>
       </c>
     </row>
@@ -4967,22 +5021,22 @@
       <c r="G14" s="9">
         <v>0.4</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="37">
         <v>74575.199999999997</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="37">
         <v>157.5</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="37">
         <v>25519.9</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="37">
         <v>22.2</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="37">
         <v>263.8</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="37">
         <v>48611.8</v>
       </c>
     </row>
@@ -5008,22 +5062,22 @@
       <c r="G15" s="9">
         <v>0.4</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="37">
         <v>66760.899999999994</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="37">
         <v>152.30000000000001</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="37">
         <v>26847.599999999999</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="37">
         <v>35.700000000000003</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="37">
         <v>361.6</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="37">
         <v>39364</v>
       </c>
     </row>
@@ -5049,22 +5103,22 @@
       <c r="G16" s="9">
         <v>0.3</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="37">
         <v>88329</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="37">
         <v>148.5</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="37">
         <v>27741</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="37">
         <v>39.700000000000003</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="37">
         <v>532.1</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="37">
         <v>59867.7</v>
       </c>
     </row>
@@ -5090,22 +5144,22 @@
       <c r="G17" s="9">
         <v>0.4</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="37">
         <v>77963.8</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="37">
         <v>131.5</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="37">
         <v>24920.400000000001</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="37">
         <v>30.6</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="37">
         <v>404.3</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="37">
         <v>52477</v>
       </c>
     </row>
@@ -5131,22 +5185,22 @@
       <c r="G18" s="9">
         <v>0.3</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="37">
         <v>82252.600000000006</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="37">
         <v>105</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="37">
         <v>27751.3</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="37">
         <v>25.5</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="37">
         <v>346.7</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="37">
         <v>54024.1</v>
       </c>
     </row>
@@ -5172,22 +5226,22 @@
       <c r="G19" s="11">
         <v>0.2</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="38">
         <v>82028.7</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="38">
         <v>75</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="38">
         <v>27696.3</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="38">
         <v>36.5</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="38">
         <v>491.5</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="38">
         <v>53729.4</v>
       </c>
     </row>
@@ -5201,9 +5255,435 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39DD8044-9C85-49FC-8BC1-16C6E08FA37D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3405655.9000000004</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2">
+        <v>18269563.600000001</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2">
+        <v>43077908.700000003</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>4151291.8000000007</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3">
+        <v>21816958.600000001</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3">
+        <v>44145028.799999997</v>
+      </c>
+      <c r="H3" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>4348566.6000000015</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4">
+        <v>24237169</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4">
+        <v>41754684.599999994</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>4845464.5999999996</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5">
+        <v>24822568.900000006</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5">
+        <v>42862530.799999982</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>3971108.4000000004</v>
+      </c>
+      <c r="D6" s="35">
+        <v>-6.7173310139758939</v>
+      </c>
+      <c r="E6">
+        <v>20986609.100000001</v>
+      </c>
+      <c r="F6" s="35">
+        <v>-8.1024175093049422</v>
+      </c>
+      <c r="G6">
+        <v>39155842.600000001</v>
+      </c>
+      <c r="H6" s="35">
+        <v>-27.283670388576695</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>4448827.5</v>
+      </c>
+      <c r="D7" s="35">
+        <v>-7.4548325370303274</v>
+      </c>
+      <c r="E7">
+        <v>22325447</v>
+      </c>
+      <c r="F7" s="35">
+        <v>-11.631517701013053</v>
+      </c>
+      <c r="G7">
+        <v>38338703.599999987</v>
+      </c>
+      <c r="H7" s="35">
+        <v>-25.002452883782382</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>4546147.1000000015</v>
+      </c>
+      <c r="D8" s="35">
+        <v>-4.700476165048002</v>
+      </c>
+      <c r="E8">
+        <v>25696291.499999993</v>
+      </c>
+      <c r="F8" s="35">
+        <v>-3.3544344933844599</v>
+      </c>
+      <c r="G8">
+        <v>43283031.099999994</v>
+      </c>
+      <c r="H8" s="35">
+        <v>-5.5056522587766779</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>5018763.7999999989</v>
+      </c>
+      <c r="D9" s="35">
+        <v>-1.6367294296033492</v>
+      </c>
+      <c r="E9">
+        <v>26476951.099999994</v>
+      </c>
+      <c r="F9" s="35">
+        <v>1.2961355459722768</v>
+      </c>
+      <c r="G9">
+        <v>43293161.899999976</v>
+      </c>
+      <c r="H9" s="35">
+        <v>-4.0791266922876304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>3956776.4000000004</v>
+      </c>
+      <c r="D10" s="35">
+        <v>-4.4687505212656475</v>
+      </c>
+      <c r="E10">
+        <v>23593687.799999997</v>
+      </c>
+      <c r="F10" s="35">
+        <v>7.7877103388459261</v>
+      </c>
+      <c r="G10">
+        <v>37614238.200000003</v>
+      </c>
+      <c r="H10" s="35">
+        <v>-7.8975065076231061</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>4785007.5999999996</v>
+      </c>
+      <c r="D11" s="35">
+        <v>3.9194203145046629</v>
+      </c>
+      <c r="E11">
+        <v>26791185.000000007</v>
+      </c>
+      <c r="F11" s="35">
+        <v>15.944835946849054</v>
+      </c>
+      <c r="G11">
+        <v>41485362.099999994</v>
+      </c>
+      <c r="H11" s="35">
+        <v>4.5483328730427246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>5263179.2999999989</v>
+      </c>
+      <c r="D12" s="35">
+        <v>10.259338380971258</v>
+      </c>
+      <c r="E12">
+        <v>28926135.899999999</v>
+      </c>
+      <c r="F12" s="35">
+        <v>7.2088587457955384</v>
+      </c>
+      <c r="G12">
+        <v>44946205.399999991</v>
+      </c>
+      <c r="H12" s="35">
+        <v>-1.1023285179260398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>5658013.5999999996</v>
+      </c>
+      <c r="D13" s="35">
+        <v>6.5568963695574922</v>
+      </c>
+      <c r="E13">
+        <v>28473216.700000003</v>
+      </c>
+      <c r="F13" s="35">
+        <v>1.6442679425148583</v>
+      </c>
+      <c r="G13">
+        <v>48338094.699999988</v>
+      </c>
+      <c r="H13" s="35">
+        <v>5.5320938472426491</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>4497675.9000000004</v>
+      </c>
+      <c r="D14" s="35">
+        <v>4.5724069762242436</v>
+      </c>
+      <c r="E14">
+        <v>25437536.699999999</v>
+      </c>
+      <c r="F14" s="35">
+        <v>-0.81415886120184666</v>
+      </c>
+      <c r="G14">
+        <v>40204590.100000001</v>
+      </c>
+      <c r="H14" s="35">
+        <v>-1.6682373690526902</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="34">
+        <v>2025</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>5344164.2999999989</v>
+      </c>
+      <c r="D15" s="35">
+        <v>3.6044498189230438</v>
+      </c>
+      <c r="E15">
+        <v>28507600.100000005</v>
+      </c>
+      <c r="F15" s="35">
+        <v>-1.2925406175648959</v>
+      </c>
+      <c r="G15">
+        <v>42764920.29999999</v>
+      </c>
+      <c r="H15" s="35">
+        <v>-4.3744334988193572</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="34">
+        <v>2025</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>6140885.7999999989</v>
+      </c>
+      <c r="D16" s="35">
+        <v>9.0433230628611625</v>
+      </c>
+      <c r="E16">
+        <v>34213884.199999996</v>
+      </c>
+      <c r="F16" s="35">
+        <v>10.54221974487912</v>
+      </c>
+      <c r="G16">
+        <v>50945081.699999988</v>
+      </c>
+      <c r="H16" s="35">
+        <v>5.931580795584722</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Real.xlsx
+++ b/data/Real.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!MDED\Comert exterior\COD_PAGE\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F7D801-5F6F-48F5-BC76-7CD73FC3193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EEE4A5-EF1D-42E0-9569-E4FBA3B0C0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Real" sheetId="1" r:id="rId1"/>
@@ -486,7 +486,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -584,6 +584,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -745,6 +748,9 @@
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="165" formatCode="[$-418]mmmm\-yy;@"/>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -755,9 +761,6 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-418]mmmm\-yy;@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="165" formatCode="[$-418]mmmm\-yy;@"/>
     </dxf>
     <dxf>
@@ -856,7 +859,7 @@
   <autoFilter ref="A1:M18" xr:uid="{4A6A945B-9F29-4D0C-8A7A-AF2D42CC98E8}"/>
   <tableColumns count="13">
     <tableColumn id="7" xr3:uid="{045D9D44-7F60-4F4E-B61F-3C4A811526D5}" name="An" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{05E6B759-F583-4594-A2AF-6E8346DD0354}" name="Trimestrul" dataDxfId="11" totalsRowDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{05E6B759-F583-4594-A2AF-6E8346DD0354}" name="Trimestrul" dataDxfId="12" totalsRowDxfId="11"/>
     <tableColumn id="2" xr3:uid="{C91398D6-47F0-4A5A-BEA2-B71364BCE39C}" name="Total mărfuri transportate, mii tone" dataDxfId="10"/>
     <tableColumn id="3" xr3:uid="{E18D51A5-C42B-444A-9D0F-BA427D9D332E}" name="Feroviar mărfuri" dataDxfId="9"/>
     <tableColumn id="4" xr3:uid="{47BED2D8-EC79-4C6C-B0F1-269C21B4A651}" name="Rutier mărfuri" dataDxfId="8"/>
@@ -1198,7 +1201,7 @@
         <v>86275.376999999993</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2">
+      <c r="D2" s="39">
         <v>13300</v>
       </c>
       <c r="E2" s="2">
@@ -1213,7 +1216,7 @@
         <v>98772.813999999998</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="2">
+      <c r="D3" s="39">
         <v>19873</v>
       </c>
       <c r="E3" s="2">
@@ -1228,7 +1231,7 @@
         <v>105480.18399999999</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2">
+      <c r="D4" s="39">
         <v>22619</v>
       </c>
       <c r="E4" s="2">
@@ -1245,7 +1248,7 @@
       <c r="C5" s="2">
         <v>39403.300000000003</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="39">
         <v>19922</v>
       </c>
       <c r="E5" s="2">
@@ -1262,7 +1265,7 @@
       <c r="C6" s="2">
         <v>43548</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="39">
         <v>23814</v>
       </c>
       <c r="E6" s="2">
@@ -1279,7 +1282,7 @@
       <c r="C7" s="2">
         <v>45654.9</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="39">
         <v>27254</v>
       </c>
       <c r="E7" s="2">
@@ -1296,7 +1299,7 @@
       <c r="C8" s="2">
         <v>47593.7</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="39">
         <v>27193</v>
       </c>
       <c r="E8" s="2">
@@ -1313,8 +1316,8 @@
       <c r="C9" s="2">
         <v>52718.460799999993</v>
       </c>
-      <c r="D9" s="2">
-        <v>30362</v>
+      <c r="D9" s="39">
+        <v>34142.400000000001</v>
       </c>
       <c r="E9" s="2">
         <v>3628.3</v>
@@ -1330,8 +1333,8 @@
       <c r="C10" s="2">
         <v>56200.5095</v>
       </c>
-      <c r="D10" s="2">
-        <v>34142.400000000001</v>
+      <c r="D10" s="39">
+        <v>32637.3</v>
       </c>
       <c r="E10" s="2">
         <v>4084.47</v>
@@ -1347,8 +1350,8 @@
       <c r="C11" s="2">
         <v>59333.121399999996</v>
       </c>
-      <c r="D11" s="2">
-        <v>32637.3</v>
+      <c r="D11" s="39">
+        <v>34597.300000000003</v>
       </c>
       <c r="E11" s="2">
         <v>4737.8100000000004</v>
@@ -1364,8 +1367,8 @@
       <c r="C12" s="2">
         <v>59659.606299999999</v>
       </c>
-      <c r="D12" s="2">
-        <v>34597.300000000003</v>
+      <c r="D12" s="39">
+        <v>30060.6</v>
       </c>
       <c r="E12" s="2">
         <v>4747.79</v>
@@ -1381,8 +1384,8 @@
       <c r="C13" s="2">
         <v>70561.767000000007</v>
       </c>
-      <c r="D13" s="2">
-        <v>30061</v>
+      <c r="D13" s="39">
+        <v>48433.5</v>
       </c>
       <c r="E13" s="2">
         <v>4800.7299999999996</v>
@@ -1398,8 +1401,8 @@
       <c r="C14" s="2">
         <v>85501.3027</v>
       </c>
-      <c r="D14" s="2">
-        <v>48434</v>
+      <c r="D14" s="39">
+        <v>41024.6</v>
       </c>
       <c r="E14" s="2">
         <v>4926.3999999999996</v>
@@ -1415,8 +1418,8 @@
       <c r="C15" s="2">
         <v>87596.523400000005</v>
       </c>
-      <c r="D15" s="2">
-        <v>41024.6</v>
+      <c r="D15" s="39">
+        <v>41800.400000000001</v>
       </c>
       <c r="E15" s="2">
         <v>5533.8572816180003</v>
@@ -1432,8 +1435,8 @@
       <c r="C16" s="2">
         <v>85957.970099999991</v>
       </c>
-      <c r="D16" s="4">
-        <v>0</v>
+      <c r="D16" s="39">
+        <v>41632.1</v>
       </c>
       <c r="E16" s="2">
         <v>5393.4</v>
@@ -1441,7 +1444,7 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="14"/>
-      <c r="D17"/>
+      <c r="D17" s="2"/>
       <c r="E17"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">

--- a/data/Real.xlsx
+++ b/data/Real.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11008"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!MDED\Comert exterior\COD_PAGE\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/air/Desktop/FrameworkData-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EEE4A5-EF1D-42E0-9569-E4FBA3B0C0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB6D49C-2DA9-2A40-96B7-BE38FE87A568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Real" sheetId="1" r:id="rId1"/>
@@ -1167,16 +1167,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.1640625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>2010</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>2907.18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2011</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>3385.91</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2012</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>3443.09</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2013</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>3380.62</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2014</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>3274.86</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>2015</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>2903.69</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>2016</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>2955.62</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>2017</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>3628.3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>2018</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>4084.47</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>2019</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>4737.8100000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>2020</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>4747.79</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>2021</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>4800.7299999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>2022</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>4926.3999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>2023</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>5533.8572816180003</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>2024</v>
       </c>
@@ -1442,34 +1442,34 @@
         <v>5393.4</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="14"/>
       <c r="D17" s="2"/>
       <c r="E17"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D18"/>
       <c r="E18"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D19"/>
       <c r="E19"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D20"/>
       <c r="E20"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="D21"/>
       <c r="E21"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="9"/>
       <c r="C22" s="24"/>
       <c r="D22"/>
       <c r="E22"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="9"/>
       <c r="C23" s="24"/>
       <c r="D23"/>
@@ -1482,26 +1482,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657D5A45-2ADC-4DD2-AEEC-998D0382C5EC}">
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="20" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="21" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="21" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="21" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" style="6" customWidth="1"/>
     <col min="10" max="10" width="27" style="6" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" style="6" customWidth="1"/>
-    <col min="12" max="12" width="20.140625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="23.5703125" style="6" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="11" max="11" width="15.83203125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="20.1640625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="23.5" style="6" customWidth="1"/>
+    <col min="14" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="19">
         <v>2010</v>
       </c>
@@ -1571,7 +1571,7 @@
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
     </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="19">
         <v>2011</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>49113443</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="19">
         <v>2012</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>54321182</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="19">
         <v>2013</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>59727533</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="19">
         <v>2014</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>65169097</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="19">
         <v>2015</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>68918204</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="19">
         <v>2016</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>81427121</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="19">
         <v>2017</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>88269381</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="19">
         <v>2018</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>97016300</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="19">
         <v>2019</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>106206042</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="19">
         <v>2020</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>103168863</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="19">
         <v>2021</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>121980026</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="19">
         <v>2022</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>134905442.75682303</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="19">
         <v>2023</v>
       </c>
@@ -2104,45 +2104,86 @@
         <v>165962292</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="19">
         <v>2024</v>
       </c>
       <c r="B16" s="9">
-        <v>323816824.35723025</v>
+        <v>323932494</v>
       </c>
       <c r="C16" s="9">
-        <v>44839012.124774933</v>
+        <v>46039035</v>
       </c>
       <c r="D16" s="9">
-        <v>23012163.955753174</v>
+        <v>23501076</v>
       </c>
       <c r="E16" s="9">
-        <v>31462281.382895026</v>
+        <v>31346877</v>
       </c>
       <c r="F16" s="9">
-        <v>22875723.335323244</v>
+        <v>23078124</v>
       </c>
       <c r="G16" s="9">
-        <v>201627643.55848387</v>
+        <v>199967381</v>
       </c>
       <c r="H16" s="9">
-        <v>303866878.96958101</v>
+        <v>304375669</v>
       </c>
       <c r="I16" s="9">
-        <v>41440182.046861708</v>
+        <v>42276395</v>
       </c>
       <c r="J16" s="9">
-        <v>17446093.651112419</v>
+        <v>17571239</v>
       </c>
       <c r="K16" s="9">
-        <v>33090132.052101489</v>
+        <v>32013786</v>
       </c>
       <c r="L16" s="9">
-        <v>22358878.983590614</v>
+        <v>22365672</v>
       </c>
       <c r="M16" s="9">
-        <v>189531592.23591474</v>
+        <v>190148575</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A17" s="19">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="9">
+        <v>353520877.2237128</v>
+      </c>
+      <c r="C17" s="9">
+        <v>50373258.570000008</v>
+      </c>
+      <c r="D17" s="9">
+        <v>26076845.407685835</v>
+      </c>
+      <c r="E17" s="9">
+        <v>34486829.225612357</v>
+      </c>
+      <c r="F17" s="9">
+        <v>25317348.663771305</v>
+      </c>
+      <c r="G17" s="9">
+        <v>217266595.35664329</v>
+      </c>
+      <c r="H17" s="9">
+        <v>331760314.22774589</v>
+      </c>
+      <c r="I17" s="9">
+        <v>46799364.30610352</v>
+      </c>
+      <c r="J17" s="9">
+        <v>26014131.659141526</v>
+      </c>
+      <c r="K17" s="9">
+        <v>32131885.410973083</v>
+      </c>
+      <c r="L17" s="9">
+        <v>24594771.423944168</v>
+      </c>
+      <c r="M17" s="9">
+        <v>202220161.42758358</v>
       </c>
     </row>
   </sheetData>
@@ -2153,23 +2194,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C86564E-7195-442B-9542-582DC2DD7756}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" style="6" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="26.140625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="6" customWidth="1"/>
-    <col min="9" max="9" width="32.140625" style="6" customWidth="1"/>
-    <col min="10" max="10" width="39.85546875" style="6" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="6" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" style="6" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="2" max="2" width="27.1640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="32.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="26.1640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="16.5" style="6" customWidth="1"/>
+    <col min="9" max="9" width="32.1640625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="39.83203125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="21.83203125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="12.5" style="6" customWidth="1"/>
+    <col min="14" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -2210,7 +2251,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="11">
         <v>2010</v>
       </c>
@@ -2251,7 +2292,7 @@
         <v>63455993</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="11">
         <v>2011</v>
       </c>
@@ -2292,7 +2333,7 @@
         <v>67050590</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="11">
         <v>2012</v>
       </c>
@@ -2333,7 +2374,7 @@
         <v>67050590</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="11">
         <v>2013</v>
       </c>
@@ -2374,7 +2415,7 @@
         <v>72587936</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="11">
         <v>2014</v>
       </c>
@@ -2415,7 +2456,7 @@
         <v>78366066</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="11">
         <v>2015</v>
       </c>
@@ -2456,7 +2497,7 @@
         <v>79966056</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" s="11">
         <v>2016</v>
       </c>
@@ -2497,7 +2538,7 @@
         <v>86065563</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="23">
         <v>2017</v>
       </c>
@@ -2538,7 +2579,7 @@
         <v>98763025</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="23">
         <v>2018</v>
       </c>
@@ -2579,7 +2620,7 @@
         <v>107051290</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="23">
         <v>2019</v>
       </c>
@@ -2620,7 +2661,7 @@
         <v>113922687</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="11">
         <v>2020</v>
       </c>
@@ -2661,7 +2702,7 @@
         <v>105299543</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="11">
         <v>2021</v>
       </c>
@@ -2702,7 +2743,7 @@
         <v>124344096</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="23">
         <v>2022</v>
       </c>
@@ -2743,7 +2784,7 @@
         <v>165455964.79498085</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="11">
         <v>2023</v>
       </c>
@@ -2784,61 +2825,92 @@
         <v>184632904</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="23">
         <v>2024</v>
       </c>
-      <c r="B16" s="23">
-        <v>323816824.35723025</v>
-      </c>
-      <c r="C16" s="23">
-        <v>275086994.44441813</v>
-      </c>
-      <c r="D16" s="23">
-        <v>63974454.459399216</v>
-      </c>
-      <c r="E16" s="23">
-        <v>68426473.386885107</v>
-      </c>
-      <c r="F16" s="23">
-        <v>101722350.65343098</v>
-      </c>
-      <c r="G16" s="23">
-        <v>185393448.58690301</v>
-      </c>
-      <c r="H16" s="23">
-        <v>303866878.96958101</v>
-      </c>
-      <c r="I16" s="23">
-        <v>261739443.1261155</v>
-      </c>
-      <c r="J16" s="23">
-        <v>58101723.493214905</v>
-      </c>
-      <c r="K16" s="23">
-        <v>70888928.054537758</v>
-      </c>
-      <c r="L16" s="23">
-        <v>101232105.54935327</v>
-      </c>
-      <c r="M16" s="23">
-        <v>188095321.25364</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="11">
+        <v>323932493</v>
+      </c>
+      <c r="C16" s="11">
+        <v>272340088</v>
+      </c>
+      <c r="D16" s="11">
+        <v>62721169</v>
+      </c>
+      <c r="E16" s="11">
+        <v>72306007</v>
+      </c>
+      <c r="F16" s="11">
+        <v>102258360</v>
+      </c>
+      <c r="G16" s="11">
+        <v>185693131</v>
+      </c>
+      <c r="H16" s="11">
+        <v>304375669</v>
+      </c>
+      <c r="I16" s="11">
+        <v>260018873</v>
+      </c>
+      <c r="J16" s="11">
+        <v>58820377</v>
+      </c>
+      <c r="K16" s="11">
+        <v>72532496</v>
+      </c>
+      <c r="L16" s="11">
+        <v>101962747</v>
+      </c>
+      <c r="M16" s="11">
+        <v>188958824</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A17" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="23">
+        <v>353520877.2237128</v>
+      </c>
+      <c r="C17" s="23">
+        <v>300009356.08950919</v>
+      </c>
+      <c r="D17" s="23">
+        <v>71105142.568807125</v>
+      </c>
+      <c r="E17" s="23">
+        <v>85501228.389784902</v>
+      </c>
+      <c r="F17" s="23">
+        <v>112249708.73371217</v>
+      </c>
+      <c r="G17" s="23">
+        <v>215344558.15117502</v>
+      </c>
+      <c r="H17" s="23">
+        <v>331760314.22774589</v>
+      </c>
+      <c r="I17" s="23">
+        <v>283292870.05448425</v>
+      </c>
+      <c r="J17" s="23">
+        <v>63457853.543153472</v>
+      </c>
+      <c r="K17" s="23">
+        <v>87297976.057874084</v>
+      </c>
+      <c r="L17" s="23">
+        <v>106714285.1402477</v>
+      </c>
+      <c r="M17" s="23">
+        <v>209002670.26515287</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B19" s="12"/>
     </row>
   </sheetData>
@@ -2849,17 +2921,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B987E26-D1E4-466C-9A2C-368AEF8862E6}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="6"/>
+    <col min="2" max="2" width="31.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -2876,7 +2948,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="11">
         <v>2011</v>
       </c>
@@ -2893,7 +2965,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="11">
         <v>2012</v>
       </c>
@@ -2910,7 +2982,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="11">
         <v>2013</v>
       </c>
@@ -2927,7 +2999,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="11">
         <v>2014</v>
       </c>
@@ -2944,7 +3016,7 @@
         <v>104.4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="11">
         <v>2015</v>
       </c>
@@ -2961,7 +3033,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="11">
         <v>2016</v>
       </c>
@@ -2978,7 +3050,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="11">
         <v>2017</v>
       </c>
@@ -2995,7 +3067,7 @@
         <v>98.3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="11">
         <v>2018</v>
       </c>
@@ -3012,7 +3084,7 @@
         <v>107.4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="11">
         <v>2019</v>
       </c>
@@ -3029,7 +3101,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="11">
         <v>2020</v>
       </c>
@@ -3046,7 +3118,7 @@
         <v>102.3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="11">
         <v>2021</v>
       </c>
@@ -3063,7 +3135,7 @@
         <v>116.1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="11">
         <v>2022</v>
       </c>
@@ -3080,7 +3152,7 @@
         <v>91.6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="11">
         <v>2023</v>
       </c>
@@ -3097,7 +3169,7 @@
         <v>105.4</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="11">
         <v>2024</v>
       </c>
@@ -3122,17 +3194,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1BFE96-3D4B-4D78-8E7A-9B4703623128}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="7.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="6" customWidth="1"/>
     <col min="3" max="3" width="26" style="6" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="6"/>
+    <col min="4" max="4" width="28.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -3149,7 +3221,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
         <v>9</v>
       </c>
@@ -3166,7 +3238,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="29" t="s">
         <v>9</v>
       </c>
@@ -3183,7 +3255,7 @@
         <v>93.3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="29" t="s">
         <v>9</v>
       </c>
@@ -3200,7 +3272,7 @@
         <v>102.1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="29" t="s">
         <v>9</v>
       </c>
@@ -3217,7 +3289,7 @@
         <v>92.1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="29" t="s">
         <v>10</v>
       </c>
@@ -3234,7 +3306,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="29" t="s">
         <v>10</v>
       </c>
@@ -3251,7 +3323,7 @@
         <v>92.6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="29" t="s">
         <v>10</v>
       </c>
@@ -3268,7 +3340,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="29" t="s">
         <v>10</v>
       </c>
@@ -3285,7 +3357,7 @@
         <v>111.4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="29" t="s">
         <v>11</v>
       </c>
@@ -3302,7 +3374,7 @@
         <v>95.1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="29" t="s">
         <v>11</v>
       </c>
@@ -3319,7 +3391,7 @@
         <v>101.10645766556515</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="29" t="s">
         <v>11</v>
       </c>
@@ -3336,7 +3408,7 @@
         <v>92.455178451931758</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="29" t="s">
         <v>11</v>
       </c>
@@ -3353,7 +3425,7 @@
         <v>109.2614196960548</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="29" t="s">
         <v>12</v>
       </c>
@@ -3370,7 +3442,7 @@
         <v>111.66741953698478</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="29" t="s">
         <v>12</v>
       </c>
@@ -3387,7 +3459,7 @@
         <v>104.4</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="29" t="s">
         <v>12</v>
       </c>
@@ -3404,7 +3476,7 @@
         <v>110.9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="29" t="s">
         <v>12</v>
       </c>
@@ -3421,7 +3493,7 @@
         <v>105.7</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="29" t="s">
         <v>13</v>
       </c>
@@ -3438,7 +3510,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="30">
         <v>2025</v>
       </c>
@@ -3455,7 +3527,7 @@
         <v>94.9</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="30">
         <v>2025</v>
       </c>
@@ -3472,10 +3544,10 @@
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="E21" s="32"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="E22" s="32"/>
     </row>
   </sheetData>
@@ -3486,35 +3558,35 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{580FE64E-7DFE-46EE-8AE6-4EC8861C505D}">
   <dimension ref="A1:AD12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.6640625" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
-    <col min="16" max="16" width="15.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="15.1640625" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="15.5" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="24.85546875" customWidth="1"/>
-    <col min="19" max="19" width="30.85546875" customWidth="1"/>
-    <col min="20" max="20" width="20.85546875" customWidth="1"/>
+    <col min="18" max="18" width="24.83203125" customWidth="1"/>
+    <col min="19" max="19" width="30.83203125" customWidth="1"/>
+    <col min="20" max="20" width="20.83203125" customWidth="1"/>
     <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="27.7109375" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" customWidth="1"/>
-    <col min="25" max="25" width="22.42578125" customWidth="1"/>
+    <col min="22" max="22" width="27.6640625" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="25" max="25" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="27" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="27" customFormat="1" ht="105" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -3596,7 +3668,7 @@
       <c r="AC1" s="22"/>
       <c r="AD1" s="22"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>2014</v>
       </c>
@@ -3673,7 +3745,7 @@
         <v>568156.69999999995</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>2015</v>
       </c>
@@ -3750,7 +3822,7 @@
         <v>589117.1</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>2016</v>
       </c>
@@ -3827,7 +3899,7 @@
         <v>535385</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>2017</v>
       </c>
@@ -3904,7 +3976,7 @@
         <v>608595.1</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>2018</v>
       </c>
@@ -3981,7 +4053,7 @@
         <v>551068.4</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>2019</v>
       </c>
@@ -4058,7 +4130,7 @@
         <v>557798.69999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>2020</v>
       </c>
@@ -4135,7 +4207,7 @@
         <v>488652.2</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>2021</v>
       </c>
@@ -4212,7 +4284,7 @@
         <v>550506.69999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>2022</v>
       </c>
@@ -4289,7 +4361,7 @@
         <v>585563</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>2023</v>
       </c>
@@ -4366,7 +4438,7 @@
         <v>586633.4</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>2024</v>
       </c>
@@ -4451,25 +4523,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5958FE6E-4604-4B72-A642-DC4E97D5FA20}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="6" customWidth="1"/>
     <col min="3" max="3" width="31" style="6" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="32.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5" style="6" customWidth="1"/>
+    <col min="8" max="8" width="32.5" style="6" customWidth="1"/>
     <col min="9" max="9" width="16" style="6" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="26.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="26.5" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="6" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" style="6" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="13" max="13" width="19.83203125" style="6" customWidth="1"/>
+    <col min="14" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="34" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -4510,7 +4582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
@@ -4551,7 +4623,7 @@
         <v>31157.7</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
@@ -4592,7 +4664,7 @@
         <v>32559.4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
@@ -4633,7 +4705,7 @@
         <v>35681.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
@@ -4674,7 +4746,7 @@
         <v>36718.5</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -4715,7 +4787,7 @@
         <v>35392.699999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
@@ -4756,7 +4828,7 @@
         <v>40758.5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -4797,7 +4869,7 @@
         <v>42262.6</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -4838,7 +4910,7 @@
         <v>46588.5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
@@ -4879,7 +4951,7 @@
         <v>46117.7</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
@@ -4920,7 +4992,7 @@
         <v>45420.3</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
@@ -4961,7 +5033,7 @@
         <v>44501.2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
@@ -5002,7 +5074,7 @@
         <v>49806.5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
         <v>12</v>
       </c>
@@ -5043,7 +5115,7 @@
         <v>48611.8</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
@@ -5084,7 +5156,7 @@
         <v>39364</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
         <v>12</v>
       </c>
@@ -5125,7 +5197,7 @@
         <v>59867.7</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
         <v>12</v>
       </c>
@@ -5166,7 +5238,7 @@
         <v>52477</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
         <v>13</v>
       </c>
@@ -5207,7 +5279,7 @@
         <v>54024.1</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19" s="10">
         <v>2025</v>
       </c>
@@ -5259,17 +5331,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39DD8044-9C85-49FC-8BC1-16C6E08FA37D}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -5295,7 +5367,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="34" t="s">
         <v>10</v>
       </c>
@@ -5321,7 +5393,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
         <v>10</v>
       </c>
@@ -5347,7 +5419,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="34" t="s">
         <v>10</v>
       </c>
@@ -5373,7 +5445,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="34" t="s">
         <v>10</v>
       </c>
@@ -5399,7 +5471,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="34" t="s">
         <v>11</v>
       </c>
@@ -5425,7 +5497,7 @@
         <v>-27.283670388576695</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="34" t="s">
         <v>11</v>
       </c>
@@ -5451,7 +5523,7 @@
         <v>-25.002452883782382</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
         <v>11</v>
       </c>
@@ -5477,7 +5549,7 @@
         <v>-5.5056522587766779</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
         <v>11</v>
       </c>
@@ -5503,7 +5575,7 @@
         <v>-4.0791266922876304</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="34" t="s">
         <v>12</v>
       </c>
@@ -5529,7 +5601,7 @@
         <v>-7.8975065076231061</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="34" t="s">
         <v>12</v>
       </c>
@@ -5555,7 +5627,7 @@
         <v>4.5483328730427246</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="34" t="s">
         <v>12</v>
       </c>
@@ -5581,7 +5653,7 @@
         <v>-1.1023285179260398</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="34" t="s">
         <v>12</v>
       </c>
@@ -5607,7 +5679,7 @@
         <v>5.5320938472426491</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
         <v>13</v>
       </c>
@@ -5633,7 +5705,7 @@
         <v>-1.6682373690526902</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="34">
         <v>2025</v>
       </c>
@@ -5659,7 +5731,7 @@
         <v>-4.3744334988193572</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="34">
         <v>2025</v>
       </c>
